--- a/Assay_Plate_Data_Template.xlsx
+++ b/Assay_Plate_Data_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://czbg.sharepoint.com/teams/CREW10/Shared Documents/Rhino/AAZV_PRL2025/Data Analysis2026/AssayVariationR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_262E471B0FDFE2359031F1A1353D01AF43B65A59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8611018D-CB0D-4251-A7C0-9359E4677A8A}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_262E471B0FDFE2359031F1A1353D01AF43B65A59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6BE3070-CC0D-46FA-A65E-24982B5F1AA6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="160">
   <si>
     <t>ASSAY PLATE METADATA TEMPLATE — INSTRUCTIONS</t>
   </si>
@@ -485,6 +485,24 @@
   </si>
   <si>
     <t>Identifier for the biological reference sample run on this plate. This would be a biological sample (e.g., pooled serum) used to track assay consistency across plates and lots. This is NOT a manufactured QC sample.</t>
+  </si>
+  <si>
+    <t>Ref2_ID</t>
+  </si>
+  <si>
+    <t>Ref2_Conc</t>
+  </si>
+  <si>
+    <t>Ref2_Signal</t>
+  </si>
+  <si>
+    <t>Identifier for a second biological reference sample run on this plate. This would be a biological sample (e.g., pooled serum) used to track assay consistency across plates and lots. This is NOT a manufactured QC sample.</t>
+  </si>
+  <si>
+    <t>Reported concentration of the second reference sample from this plate. NOT corrected for dilution factor.</t>
+  </si>
+  <si>
+    <t>Signal value (e.g., %B or OD) for the second reference sample on this plate.</t>
   </si>
 </sst>
 </file>
@@ -935,219 +953,219 @@
     <tabColor rgb="FF548235"/>
   </sheetPr>
   <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:1" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
     </row>
-    <row r="39" spans="1:1" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>27</v>
       </c>
@@ -1159,8 +1177,501 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AG1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="11" width="12" customWidth="1"/>
+    <col min="12" max="31" width="10" customWidth="1"/>
+    <col min="32" max="32" width="13" customWidth="1"/>
+    <col min="33" max="33" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG1" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Curve Model" error="Please select 4PL, 5PL, or Linear" promptTitle="Curve Model" prompt="Select the curve model used by the instrument software" sqref="AF2:AF500" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"4PL,5PL,Linear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Signal Units" error="Select a signal unit or type a custom value" sqref="H2:K500" xr:uid="{00000000-0002-0000-0100-000001000000}">
+      <formula1>"%B,OD,RLU,MFI"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF2F5496"/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:AD13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1173,440 +1684,7 @@
     <col min="30" max="30" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Curve Model" error="Please select 4PL, 5PL, or Linear" promptTitle="Curve Model" prompt="Select the curve model used by the instrument software" sqref="AC2:AC500" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"4PL,5PL,Linear"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Signal Units" error="Select a signal unit or type a custom value" sqref="H2:H500" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"%B,OD,RLU,MFI"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF2F5496"/>
-  </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
-  <dimension ref="A1:AD13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="28" width="10" customWidth="1"/>
-    <col min="29" max="29" width="13" customWidth="1"/>
-    <col min="30" max="30" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>105</v>
       </c>
@@ -1640,7 +1718,7 @@
       <c r="AC1" s="11"/>
       <c r="AD1" s="11"/>
     </row>
-    <row r="2" spans="1:30" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
@@ -1732,7 +1810,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>106</v>
       </c>
@@ -1766,7 +1844,7 @@
       <c r="AC3" s="11"/>
       <c r="AD3" s="11"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>107</v>
       </c>
@@ -1852,7 +1930,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>118</v>
       </c>
@@ -1886,7 +1964,7 @@
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>119</v>
       </c>
@@ -1966,7 +2044,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>127</v>
       </c>
@@ -2000,7 +2078,7 @@
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
     </row>
-    <row r="10" spans="1:30" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>128</v>
       </c>
@@ -2078,7 +2156,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>137</v>
       </c>
@@ -2112,7 +2190,7 @@
       <c r="AC12" s="11"/>
       <c r="AD12" s="11"/>
     </row>
-    <row r="13" spans="1:30" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>138</v>
       </c>
@@ -2205,6 +2283,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0233932-4c4e-4826-91aa-0aacca315d69" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dcabd06-856b-4822-94b1-3a08ab73ca3d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <bydate xmlns="3dcabd06-856b-4822-94b1-3a08ab73ca3d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AF86970C261174591DD0E9E45FBEE83" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0379a14d0134a7bea9107749466b0690">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3dcabd06-856b-4822-94b1-3a08ab73ca3d" xmlns:ns3="d0233932-4c4e-4826-91aa-0aacca315d69" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b4d024ff8289acf3d96f77a36d43b8d" ns2:_="" ns3:_="">
     <xsd:import namespace="3dcabd06-856b-4822-94b1-3a08ab73ca3d"/>
@@ -2459,28 +2558,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B59C045-D775-42DC-A469-44F06E55BA2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0233932-4c4e-4826-91aa-0aacca315d69"/>
+    <ds:schemaRef ds:uri="3dcabd06-856b-4822-94b1-3a08ab73ca3d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0233932-4c4e-4826-91aa-0aacca315d69" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dcabd06-856b-4822-94b1-3a08ab73ca3d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <bydate xmlns="3dcabd06-856b-4822-94b1-3a08ab73ca3d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82DB9B68-C0EF-4573-B69F-286B6B094721}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C22DA334-2BB1-4434-A683-5B651BF4B9E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2497,23 +2594,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82DB9B68-C0EF-4573-B69F-286B6B094721}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B59C045-D775-42DC-A469-44F06E55BA2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0233932-4c4e-4826-91aa-0aacca315d69"/>
-    <ds:schemaRef ds:uri="3dcabd06-856b-4822-94b1-3a08ab73ca3d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Assay_Plate_Data_Template.xlsx
+++ b/Assay_Plate_Data_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://czbg.sharepoint.com/teams/CREW10/Shared Documents/Rhino/AAZV_PRL2025/Data Analysis2026/AssayVariationR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lrispoli\Documents\R\AssayVariationR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_262E471B0FDFE2359031F1A1353D01AF43B65A59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6BE3070-CC0D-46FA-A65E-24982B5F1AA6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432FBD9B-0465-4377-A9AE-AF86C296BBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="159">
   <si>
     <t>ASSAY PLATE METADATA TEMPLATE — INSTRUCTIONS</t>
   </si>
@@ -94,9 +94,6 @@
     <t>CURVE MODEL</t>
   </si>
   <si>
-    <t>Record the regression model the instrument software used to fit the standard curve for that plate. A dropdown is provided with three options: 4PL (four-parameter logistic), 5PL (five-parameter logistic), and Linear. The R Markdown pipeline uses this field diagnostically — if its independent curve fit disagrees with the recorded model, that discrepancy will be flagged.</t>
-  </si>
-  <si>
     <t>TIPS FOR RETROSPECTIVE DATA ENTRY</t>
   </si>
   <si>
@@ -328,9 +325,6 @@
     <t>Character (dropdown)</t>
   </si>
   <si>
-    <t>4PL = four-parameter logistic; 5PL = five-parameter logistic (adds asymmetry parameter); Linear = simple linear regression. Select from dropdown.</t>
-  </si>
-  <si>
     <t>Free-text field for any relevant information about the plate.</t>
   </si>
   <si>
@@ -457,9 +451,6 @@
     <t>POOL-A</t>
   </si>
   <si>
-    <t>Linear</t>
-  </si>
-  <si>
     <t>In-house cortisol EIA; linear fit used by software for this lot</t>
   </si>
   <si>
@@ -503,6 +494,12 @@
   </si>
   <si>
     <t>Signal value (e.g., %B or OD) for the second reference sample on this plate.</t>
+  </si>
+  <si>
+    <t>4PL = four-parameter logistic; 5PL = five-parameter logistic (adds asymmetry parameter). Select from dropdown.</t>
+  </si>
+  <si>
+    <t>Record the regression model the instrument software used to fit the standard curve for that plate. A dropdown is provided with two options: 4PL (four-parameter logistic) or 5PL (five-parameter logistic). The R Markdown pipeline uses this field diagnostically — if its independent curve fit disagrees with the recorded model, that discrepancy will be flagged.</t>
   </si>
 </sst>
 </file>
@@ -986,7 +983,7 @@
     </row>
     <row r="7" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -1043,7 +1040,7 @@
     </row>
     <row r="20" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -1056,7 +1053,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -1118,7 +1115,7 @@
     </row>
     <row r="37" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
@@ -1126,7 +1123,7 @@
     </row>
     <row r="39" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
@@ -1139,7 +1136,7 @@
     </row>
     <row r="42" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -1147,27 +1144,27 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1193,112 +1190,112 @@
   <sheetData>
     <row r="1" spans="1:33" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="AG1" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Curve Model" error="Please select 4PL, 5PL, or Linear" promptTitle="Curve Model" prompt="Select the curve model used by the instrument software" sqref="AF2:AF500" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"4PL,5PL,Linear"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" errorTitle="Signal Units" error="Select a signal unit or type a custom value" sqref="H2:K500" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"%B,OD,RLU,MFI"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Curve Model" error="Please select 4PL, 5PL, or Linear" promptTitle="Curve Model" prompt="Select the curve model used by the instrument software" sqref="AF2:AF1048576" xr:uid="{9E74517E-3C9B-47F5-93CE-13480BA3E24A}">
+      <formula1>"4PL,5PL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1322,342 +1319,342 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>157</v>
-      </c>
       <c r="C13" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="C14" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="C15" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="E15" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="6" t="s">
+    </row>
+    <row r="19" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>100</v>
-      </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1686,7 +1683,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1720,99 +1717,99 @@
     </row>
     <row r="2" spans="1:30" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1846,31 +1843,31 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="J4" s="9">
         <v>0.17599999999999999</v>
@@ -1924,15 +1921,15 @@
       </c>
       <c r="AB4" s="9"/>
       <c r="AC4" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AD4" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1966,31 +1963,31 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="F7" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="J7" s="9">
         <v>8.1129999999999995</v>
@@ -2038,15 +2035,15 @@
       <c r="AA7" s="9"/>
       <c r="AB7" s="9"/>
       <c r="AC7" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -2080,28 +2077,28 @@
     </row>
     <row r="10" spans="1:30" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>133</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -2150,15 +2147,15 @@
       <c r="AA10" s="9"/>
       <c r="AB10" s="9"/>
       <c r="AC10" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2192,31 +2189,31 @@
     </row>
     <row r="13" spans="1:30" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="E13" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="G13" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>143</v>
       </c>
       <c r="J13" s="9">
         <v>5.32</v>
@@ -2264,10 +2261,10 @@
       <c r="AA13" s="9"/>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="AD13" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2283,27 +2280,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0233932-4c4e-4826-91aa-0aacca315d69" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dcabd06-856b-4822-94b1-3a08ab73ca3d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <bydate xmlns="3dcabd06-856b-4822-94b1-3a08ab73ca3d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AF86970C261174591DD0E9E45FBEE83" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0379a14d0134a7bea9107749466b0690">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3dcabd06-856b-4822-94b1-3a08ab73ca3d" xmlns:ns3="d0233932-4c4e-4826-91aa-0aacca315d69" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b4d024ff8289acf3d96f77a36d43b8d" ns2:_="" ns3:_="">
     <xsd:import namespace="3dcabd06-856b-4822-94b1-3a08ab73ca3d"/>
@@ -2558,26 +2534,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B59C045-D775-42DC-A469-44F06E55BA2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0233932-4c4e-4826-91aa-0aacca315d69"/>
-    <ds:schemaRef ds:uri="3dcabd06-856b-4822-94b1-3a08ab73ca3d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82DB9B68-C0EF-4573-B69F-286B6B094721}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0233932-4c4e-4826-91aa-0aacca315d69" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dcabd06-856b-4822-94b1-3a08ab73ca3d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <bydate xmlns="3dcabd06-856b-4822-94b1-3a08ab73ca3d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C22DA334-2BB1-4434-A683-5B651BF4B9E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2594,4 +2572,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82DB9B68-C0EF-4573-B69F-286B6B094721}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B59C045-D775-42DC-A469-44F06E55BA2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0233932-4c4e-4826-91aa-0aacca315d69"/>
+    <ds:schemaRef ds:uri="3dcabd06-856b-4822-94b1-3a08ab73ca3d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>